--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_43.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2788524.710881341</v>
+        <v>2781657.717932685</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034356</v>
+        <v>10041900.99034355</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900416</v>
+        <v>286.4107162896426</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900416</v>
+        <v>286.4107162896426</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>141.7804375265674</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>305.214484270644</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>119.040440756494</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>39.04534712526427</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>148.6880250402009</v>
       </c>
     </row>
     <row r="7">
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1210,22 +1210,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>199.8180013219744</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751173017</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F11" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
         <v>53.75737228701621</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>115.0662319853481</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
@@ -1854,13 +1854,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H17" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>206.6512890796133</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2158,16 +2158,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096173</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T21" t="n">
         <v>55.35776521751382</v>
@@ -2316,7 +2316,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D23" t="n">
         <v>60.33915573984979</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2395,13 +2395,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T24" t="n">
         <v>55.35776521751382</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2629,22 +2629,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176916</v>
       </c>
       <c r="C27" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>53.75737228701621</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>86.93822665041519</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X30" t="n">
-        <v>132.5405019708301</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>49.39139276613435</v>
@@ -3039,13 +3039,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H32" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>11.09991244551929</v>
+        <v>75.83998807325922</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V33" t="n">
         <v>64.51066719152016</v>
@@ -3276,7 +3276,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F36" t="n">
-        <v>86.93822665041522</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3516,10 +3516,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3817,10 +3817,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>115.0662319853481</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>579.1494159256323</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4430,22 +4430,22 @@
         <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>406.5182159771517</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>98.22075711791538</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>83.56351753052128</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>50.86337317715914</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>802.2142818821733</v>
+        <v>256.125934252978</v>
       </c>
       <c r="C4" t="n">
-        <v>928.2162877006091</v>
+        <v>256.125934252978</v>
       </c>
       <c r="D4" t="n">
-        <v>1041.535431825609</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>1159.364336037022</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>1283.725308628957</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
-        <v>1437.131874515843</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H4" t="n">
-        <v>1540</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4488,19 +4488,19 @@
         <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4518,13 +4518,13 @@
         <v>256.125934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>428.0168525126554</v>
+        <v>256.125934252978</v>
       </c>
       <c r="X4" t="n">
-        <v>579.0476435368489</v>
+        <v>256.125934252978</v>
       </c>
       <c r="Y4" t="n">
-        <v>690.4569442158812</v>
+        <v>256.125934252978</v>
       </c>
     </row>
     <row r="5">
@@ -4540,25 +4540,25 @@
         <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="K5" t="n">
         <v>396.55</v>
@@ -4567,16 +4567,16 @@
         <v>396.55</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>396.55</v>
       </c>
       <c r="N5" t="n">
         <v>777.6999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>897.189519579215</v>
+        <v>746.9995952961838</v>
       </c>
       <c r="C6" t="n">
-        <v>897.189519579215</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4682,7 +4682,7 @@
         <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>897.189519579215</v>
+        <v>746.9995952961838</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>643.3896592774172</v>
+        <v>735.5658222069326</v>
       </c>
       <c r="C7" t="n">
-        <v>643.3896592774172</v>
+        <v>861.5678280253684</v>
       </c>
       <c r="D7" t="n">
-        <v>643.3896592774172</v>
+        <v>974.8869721503685</v>
       </c>
       <c r="E7" t="n">
-        <v>761.2185634888302</v>
+        <v>1092.715876361782</v>
       </c>
       <c r="F7" t="n">
-        <v>885.5795360807657</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="G7" t="n">
-        <v>1038.986101967651</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="H7" t="n">
-        <v>1208.502687127049</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>643.3896592774172</v>
+        <v>189.4774745777372</v>
       </c>
       <c r="W7" t="n">
-        <v>643.3896592774172</v>
+        <v>361.3683928374146</v>
       </c>
       <c r="X7" t="n">
-        <v>643.3896592774172</v>
+        <v>512.3991838616081</v>
       </c>
       <c r="Y7" t="n">
-        <v>643.3896592774172</v>
+        <v>623.8084845406404</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
@@ -4810,37 +4810,37 @@
         <v>1174.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
       </c>
       <c r="R8" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S8" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W8" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4853,19 +4853,19 @@
         <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>897.189519579215</v>
+        <v>720.0003429896865</v>
       </c>
       <c r="D9" t="n">
-        <v>897.189519579215</v>
+        <v>720.0003429896865</v>
       </c>
       <c r="E9" t="n">
-        <v>897.189519579215</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>695.3531546075237</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>912.9840961492151</v>
+        <v>969.1815371836198</v>
       </c>
       <c r="C10" t="n">
-        <v>1038.986101967651</v>
+        <v>1095.183543002056</v>
       </c>
       <c r="D10" t="n">
-        <v>1038.986101967651</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="E10" t="n">
-        <v>1038.986101967651</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="F10" t="n">
-        <v>1038.986101967651</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="G10" t="n">
-        <v>1038.986101967651</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="H10" t="n">
-        <v>1208.502687127049</v>
+        <v>1208.502687127056</v>
       </c>
       <c r="I10" t="n">
-        <v>1429.635566063132</v>
+        <v>1429.635566063139</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063132</v>
+        <v>1429.635566063139</v>
       </c>
       <c r="K10" t="n">
-        <v>1540</v>
+        <v>1540.000000000007</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>52.08501657461284</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>240.1606957334177</v>
       </c>
       <c r="U10" t="n">
-        <v>277.3511926382866</v>
+        <v>486.7118883717043</v>
       </c>
       <c r="V10" t="n">
-        <v>476.1725855242326</v>
+        <v>685.5332812576503</v>
       </c>
       <c r="W10" t="n">
-        <v>538.7866667796973</v>
+        <v>857.4241995173277</v>
       </c>
       <c r="X10" t="n">
-        <v>689.8174578038908</v>
+        <v>857.4241995173277</v>
       </c>
       <c r="Y10" t="n">
-        <v>801.2267584829231</v>
+        <v>857.4241995173277</v>
       </c>
     </row>
     <row r="11">
@@ -5020,13 +5020,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5035,22 +5035,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>1243.990904947333</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C12" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D12" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E12" t="n">
         <v>380.2433203903244</v>
@@ -5272,19 +5272,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N14" t="n">
         <v>1500.287941766591</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2053.697941766591</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2236</v>
       </c>
       <c r="P14" t="n">
         <v>2236</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D15" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E15" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5378,22 +5378,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="16">
@@ -5403,28 +5403,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C16" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D16" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H16" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I16" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J16" t="n">
         <v>1860.696627021627</v>
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U16" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V16" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W16" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X16" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y16" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="17">
@@ -5497,34 +5497,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1243.990904947333</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>264.0395817084329</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D18" t="n">
-        <v>264.0395817084329</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5630,7 +5630,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="19">
@@ -5694,13 +5694,13 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
         <v>644.3484002705077</v>
@@ -5746,16 +5746,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1286.552076218397</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1797.400904947332</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
         <v>1797.400904947332</v>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5849,25 +5849,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="22">
@@ -5959,19 +5959,19 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,25 +5980,25 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>555.568828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6038,10 +6038,10 @@
         <v>119.2429040110725</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E24" t="n">
         <v>44.72</v>
@@ -6086,25 +6086,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X24" t="n">
         <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>154.1485167851398</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="25">
@@ -6123,7 +6123,7 @@
         <v>1018.077762255669</v>
       </c>
       <c r="E25" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F25" t="n">
         <v>1153.55685638681</v>
@@ -6193,49 +6193,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C26" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D26" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E26" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F26" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G26" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K26" t="n">
-        <v>690.5809049473327</v>
+        <v>44.72</v>
       </c>
       <c r="L26" t="n">
-        <v>1243.990904947333</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M26" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N26" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U26" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V26" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W26" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X26" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y26" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="27">
@@ -6272,19 +6272,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
         <v>44.72</v>
@@ -6442,13 +6442,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>733.1420762183976</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="L29" t="n">
-        <v>733.1420762183976</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M29" t="n">
-        <v>1243.990904947333</v>
+        <v>1129.18</v>
       </c>
       <c r="N29" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>132.5363905559749</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6575,10 +6575,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>494.2632948060406</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>444.3729990826726</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6682,31 +6682,31 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K32" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L32" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M32" t="n">
-        <v>946.8779417665908</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N32" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O32" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
         <v>1797.400904947332</v>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D33" t="n">
         <v>44.72</v>
@@ -6797,25 +6797,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="34">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
         <v>103.3156148520479</v>
@@ -6928,52 +6928,52 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>179.7320762183977</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="N35" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O35" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6992,10 +6992,10 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F36" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7128,10 +7128,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7159,7 +7159,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7168,22 +7168,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N38" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>297.950717050992</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1025.324879873102</v>
       </c>
       <c r="R39" t="n">
-        <v>826.0584179616072</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S39" t="n">
-        <v>708.3170038559392</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T39" t="n">
-        <v>652.400069292794</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U39" t="n">
-        <v>601.6825341814942</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V39" t="n">
-        <v>536.5202440890496</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>453.3150492306369</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>382.7466255484273</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>332.8563298250593</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,31 +7299,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K40" t="n">
         <v>1921.561060958496</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7402,19 +7402,19 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M41" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
         <v>1797.400904947332</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V42" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7593,19 +7593,19 @@
         <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7645,46 +7645,46 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M44" t="n">
+        <v>946.8779417665908</v>
+      </c>
+      <c r="N44" t="n">
         <v>1500.287941766591</v>
       </c>
-      <c r="N44" t="n">
-        <v>2053.697941766591</v>
-      </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>391.4553531635761</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>404.4874506895348</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>385.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8453,13 +8453,13 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>542.2671287719298</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,13 +8678,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1036.248958069835</v>
@@ -8693,10 +8693,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8927,10 +8927,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>254.3913627391524</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q14" t="n">
         <v>172.8226843274854</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,19 +9389,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>300.1141042229713</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>206.6237041381304</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,7 +10100,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>300.1141042229715</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10349,10 +10349,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,16 +10571,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
@@ -10589,10 +10589,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10823,13 +10823,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>370.3619737970638</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>801.385149773304</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,13 +11297,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>254.3913627391524</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.5911706460559</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646049022</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26305,13 +26305,13 @@
         <v>1353830.31835754</v>
       </c>
       <c r="N2" t="n">
-        <v>1353830.318357541</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="O2" t="n">
         <v>1353830.31835754</v>
       </c>
       <c r="P2" t="n">
-        <v>1353830.31835754</v>
+        <v>1353830.318357541</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>590319.5412553627</v>
+        <v>588803.6855670473</v>
       </c>
       <c r="C6" t="n">
-        <v>727897.5213891774</v>
+        <v>726381.6657008611</v>
       </c>
       <c r="D6" t="n">
-        <v>729958.2933014926</v>
+        <v>728442.437613177</v>
       </c>
       <c r="E6" t="n">
-        <v>406076.9151310049</v>
+        <v>404335.0653178975</v>
       </c>
       <c r="F6" t="n">
-        <v>749267.810476509</v>
+        <v>747525.9606634016</v>
       </c>
       <c r="G6" t="n">
-        <v>751213.3869446948</v>
+        <v>749471.5371315872</v>
       </c>
       <c r="H6" t="n">
-        <v>753161.6637619961</v>
+        <v>751419.8139488884</v>
       </c>
       <c r="I6" t="n">
-        <v>755112.6604053563</v>
+        <v>753370.8105922485</v>
       </c>
       <c r="J6" t="n">
-        <v>341546.3966069812</v>
+        <v>339804.5467938735</v>
       </c>
       <c r="K6" t="n">
-        <v>759022.8923592009</v>
+        <v>757281.0425460931</v>
       </c>
       <c r="L6" t="n">
-        <v>760982.1679194601</v>
+        <v>759240.3181063524</v>
       </c>
       <c r="M6" t="n">
-        <v>701696.2438154392</v>
+        <v>699954.394002332</v>
       </c>
       <c r="N6" t="n">
-        <v>764909.1408502933</v>
+        <v>763167.291037185</v>
       </c>
       <c r="O6" t="n">
-        <v>486876.8801080312</v>
+        <v>485135.030294923</v>
       </c>
       <c r="P6" t="n">
-        <v>768847.4829590409</v>
+        <v>767105.633145934</v>
       </c>
     </row>
   </sheetData>
@@ -26999,13 +26999,13 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27014,7 +27014,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -27039,31 +27039,31 @@
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
         <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27106,13 +27106,13 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>197.8558048113095</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>94.99587548954275</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>311.9806467141294</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27609,16 +27609,16 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>332.6783235603633</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27654,13 +27654,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,10 +27752,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>250.7033677259334</v>
       </c>
     </row>
     <row r="7">
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27849,13 +27849,13 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
+        <v>359.4505875674658</v>
+      </c>
+      <c r="W7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>400</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>341.30418131334</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27989,22 +27989,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>185.682627621886</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>139.8182410159025</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28071,7 +28071,7 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28083,7 +28083,7 @@
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28116,10 +28116,10 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>383.8734964448886</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28128,13 +28128,13 @@
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>289.6193565614013</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28156,7 +28156,7 @@
         <v>350</v>
       </c>
       <c r="F11" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G11" t="n">
         <v>350</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
@@ -28232,7 +28232,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>262.1624218828912</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28466,13 +28466,13 @@
         <v>350</v>
       </c>
       <c r="D15" t="n">
-        <v>274.8961667101369</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>276.9584798124345</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28514,7 +28514,7 @@
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
@@ -28563,7 +28563,7 @@
         <v>350</v>
       </c>
       <c r="J16" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28633,13 +28633,13 @@
         <v>350</v>
       </c>
       <c r="G17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H17" t="n">
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,13 +28700,13 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28839,7 +28839,7 @@
         <v>350</v>
       </c>
       <c r="W19" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X19" t="n">
         <v>350</v>
@@ -28937,16 +28937,16 @@
         <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -28985,7 +28985,7 @@
         <v>350</v>
       </c>
       <c r="S21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>350</v>
@@ -29095,22 +29095,22 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
+        <v>350</v>
+      </c>
+      <c r="D23" t="n">
+        <v>350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>350</v>
+      </c>
+      <c r="F23" t="n">
+        <v>350</v>
+      </c>
+      <c r="G23" t="n">
+        <v>350</v>
+      </c>
+      <c r="H23" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="D23" t="n">
-        <v>350</v>
-      </c>
-      <c r="E23" t="n">
-        <v>350</v>
-      </c>
-      <c r="F23" t="n">
-        <v>350</v>
-      </c>
-      <c r="G23" t="n">
-        <v>350</v>
-      </c>
-      <c r="H23" t="n">
-        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29174,13 +29174,13 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29222,7 +29222,7 @@
         <v>350</v>
       </c>
       <c r="S24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>350</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29259,10 +29259,10 @@
         <v>350</v>
       </c>
       <c r="E25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="F25" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29408,22 +29408,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>255.7338705714974</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H27" t="n">
         <v>332.1680871864211</v>
@@ -29578,7 +29578,7 @@
         <v>350</v>
       </c>
       <c r="F29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G29" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29648,7 +29648,7 @@
         <v>350</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29660,10 +29660,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29711,7 +29711,7 @@
         <v>350</v>
       </c>
       <c r="X30" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="Y30" t="n">
         <v>350</v>
@@ -29818,13 +29818,13 @@
         <v>350</v>
       </c>
       <c r="G32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,10 +29885,10 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -29933,13 +29933,13 @@
         <v>350</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
       </c>
       <c r="U33" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V33" t="n">
         <v>350</v>
@@ -30055,7 +30055,7 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30128,13 +30128,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F36" t="n">
-        <v>252.6980156874616</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30264,7 +30264,7 @@
         <v>350</v>
       </c>
       <c r="X37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y37" t="n">
         <v>350</v>
@@ -30295,10 +30295,10 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>103.0735997869498</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30404,7 +30404,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30596,10 +30596,10 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>285.2599243722601</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30729,7 +30729,7 @@
         <v>350</v>
       </c>
       <c r="U43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>269.4903246609786</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>26.44442865857389</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34895,16 +34895,16 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>103.9071974587446</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34940,13 +34940,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>385</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="P5" t="n">
         <v>385</v>
       </c>
       <c r="Q5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35135,13 +35135,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>142.1338710971238</v>
+        <v>160.2802773512497</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35232,13 +35232,13 @@
         <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,7 +35357,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35369,7 +35369,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>21.50001674203317</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
@@ -35414,13 +35414,13 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>63.24654672269158</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,13 +35457,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>559</v>
@@ -35472,10 +35472,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35706,10 +35706,10 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
+        <v>559</v>
+      </c>
+      <c r="P14" t="n">
         <v>184.1434931650599</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35849,7 +35849,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J16" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K16" t="n">
         <v>61.47922619885696</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N17" t="n">
         <v>559</v>
       </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>559</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36125,7 +36125,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X19" t="n">
         <v>102.5563545698924</v>
@@ -36168,19 +36168,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>300.1141042229713</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36545,10 +36545,10 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>61.23042579717762</v>
+        <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G25" t="n">
         <v>104.95612715847</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,7 +36879,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>300.1141042229715</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -37128,10 +37128,10 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P32" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37350,16 +37350,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
@@ -37368,10 +37368,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37550,7 +37550,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y37" t="n">
         <v>62.53464715053764</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -37602,13 +37602,13 @@
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>300.1141042229714</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38015,7 +38015,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V43" t="n">
         <v>150.8296897837838</v>
@@ -38067,7 +38067,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,13 +38076,13 @@
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>184.1434931650599</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
